--- a/saved/0 LOGS-d1-b5-6-00.xlsx
+++ b/saved/0 LOGS-d1-b5-6-00.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 06:30:00</t>
+          <t>2026-05-14 06:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pc3</t>
+          <t>pc1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -572,271 +572,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>победа</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-14 06:30:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pc2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>108</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ec1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>108</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>side_attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-14 07:00:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pc2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>108</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ec3p1s1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>засада</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-14 08:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pc1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>85</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ec1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>108</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>поражение</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-14 08:00:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>pc3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>86</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ec1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>108</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>inf_attacks_inf</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>side_attack</t>
+          <t>ничья</t>
         </is>
       </c>
     </row>
